--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -751,7 +751,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1079,10 +1079,8 @@
           <t>Rohit Kumar Raut</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9821137517</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9821137517</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -1168,10 +1166,8 @@
           <t>Om Neupane</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
@@ -1182,7 +1178,7 @@
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : no light on the router  has been updated by Om Neupane</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -544,20 +544,38 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -572,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -628,7 +646,30 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -643,12 +684,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -664,6 +706,11 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
           <t>Grand Total</t>
         </is>
       </c>
@@ -677,21 +724,43 @@
       <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C4" s="4" t="n">
         <v>1</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -705,23 +774,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX2"/>
+  <dimension ref="A1:AX3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -738,26 +807,26 @@
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="42" customWidth="1" min="31" max="31"/>
-    <col width="16" customWidth="1" min="32" max="32"/>
+    <col width="45" customWidth="1" min="31" max="31"/>
+    <col width="23" customWidth="1" min="32" max="32"/>
     <col width="30" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="15" customWidth="1" min="38" max="38"/>
-    <col width="19" customWidth="1" min="39" max="39"/>
+    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
-    <col width="16" customWidth="1" min="50" max="50"/>
+    <col width="23" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1212,6 +1281,222 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 9:15 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352600</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Dhanishwar Subedi</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Dhanishwar Subedi</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9851159410</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:15:18 AM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>9851159410</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 01:00:32 PM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:15:18 AM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>27.68338</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>Open Korean Bhasa - Language school Bhaktapur 44800, Bhaktapur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>dhsubedi03@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>07:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>2,6</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>85.30336</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>20h 14m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -820,7 +820,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1348,10 +1348,8 @@
           <t>Dhanishwar Subedi</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9851159410</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9851159410</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1386,10 +1384,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>27.68338</t>
-        </is>
+      <c r="Y3" s="3" t="n">
+        <v>27.68338</v>
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
@@ -1445,25 +1441,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>2,6</t>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>85.30336</t>
-        </is>
+      <c r="AP3" s="3" t="n">
+        <v>85.30336</v>
       </c>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,7 +528,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Om Neupane</t>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -546,36 +546,54 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Om Neupane</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="4" t="n">
+      <c r="B5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -590,7 +608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -646,30 +664,53 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>WiFi 6 Upgrade</t>
+          <t>IPTV Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>50.0%</t>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -684,13 +725,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -701,15 +743,20 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Om Neupane</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -718,7 +765,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -727,14 +774,17 @@
       <c r="C2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -743,24 +793,49 @@
       <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="4" t="n">
-        <v>2</v>
+      <c r="D5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -774,7 +849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX3"/>
+  <dimension ref="A1:AX4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -814,13 +889,13 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="22" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1489,6 +1564,218 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 9:37 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>IPTV ISSUE</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352510</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Barjachrya</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Barjachrya</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9841255601</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:37:33 AM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>CHB9841255601</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:05:06 PM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:37:33 AM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Lazimpat, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh@gamil.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr"/>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Bishwojeet Adhikari</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>CDB328</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>21h 32m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -564,7 +564,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -580,20 +580,38 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
+      <c r="B6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -664,7 +682,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -687,7 +705,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -698,10 +716,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -710,7 +728,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -725,14 +743,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -753,10 +772,15 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -765,57 +789,66 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="6" t="n">
         <v>1</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -835,7 +868,10 @@
         <v>1</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -849,11 +885,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX4"/>
+  <dimension ref="A1:AX5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -1621,20 +1657,14 @@
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Rajesh Barjachrya</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9841255601</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9841255601</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1669,10 +1699,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1724,55 +1752,267 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>CDB328</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>21h 32m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
           <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS4" s="3" t="inlineStr">
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 10:01 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352535</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Bijay Tuladhar</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Bijay Tuladhar</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9860088963</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 10:01:43 AM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>LTP9849694056</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:20:00 PM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 10:01:43 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Bungmati, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>test@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>07:41 hour</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>L9-CDB4</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
-          <t>21h 32m</t>
-        </is>
-      </c>
-      <c r="AU4" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV4" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="AW4" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
-        </is>
-      </c>
-      <c r="AX4" s="3" t="inlineStr">
-        <is>
-          <t>Ajit Shrestha</t>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>21h 41m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -931,7 +931,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1867,10 +1867,8 @@
           <t>Bijay Tuladhar</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9860088963</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9860088963</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1905,10 +1903,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
@@ -1964,25 +1960,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>L9-CDB4</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -582,36 +582,54 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="C6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" s="4" t="n">
+      <c r="B7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -682,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -705,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -728,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -743,15 +761,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -777,10 +796,15 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -802,9 +826,12 @@
         <v>1</v>
       </c>
       <c r="E2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="G2" s="6" t="n">
         <v>2</v>
       </c>
     </row>
@@ -826,52 +853,86 @@
       <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
+          <t>Other / Uncategorized</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
           <t>Router Adaptor damage Issue</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="3" t="n">
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="6" t="n">
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>4</v>
+      <c r="F6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -885,7 +946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX5"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2008,6 +2069,114 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 10:39 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="inlineStr"/>
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr"/>
+      <c r="V6" s="3" t="inlineStr"/>
+      <c r="W6" s="3" t="inlineStr"/>
+      <c r="X6" s="3" t="inlineStr"/>
+      <c r="Y6" s="3" t="inlineStr"/>
+      <c r="Z6" s="3" t="inlineStr"/>
+      <c r="AA6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr"/>
+      <c r="AC6" s="3" t="inlineStr"/>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr"/>
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr"/>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr"/>
+      <c r="AM6" s="3" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr"/>
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
     </row>
@@ -711,14 +711,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -734,14 +734,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -761,10 +761,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -823,7 +823,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>0</v>
@@ -832,7 +832,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -863,7 +863,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -888,20 +888,20 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -911,28 +911,78 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>5</v>
+      <c r="D8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -946,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX6"/>
+  <dimension ref="A1:AX11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -959,10 +1009,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -976,12 +1026,12 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="23" customWidth="1" min="32" max="32"/>
-    <col width="30" customWidth="1" min="33" max="33"/>
+    <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -992,7 +1042,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2177,6 +2227,1062 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:27 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>slow issue</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352969</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Naresh Acharya</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Naresh Acharya</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9842295764</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 05:11:10 PM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9823137550</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:49:39 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:27:22 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>27.67706</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Koteshwor,Shatya Sai baba Marg,House nu -46,Near Suprim Overseas Pvt Ltd,and Khaja Ghar, At Bindabas</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>acnares2@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>85.3458</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>18h 16m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>18h 37m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:42 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv related issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>iptv related issue</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352779</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Narayan kumar khatri</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Narayan kumar khatri</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9860469366</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:42:05 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>KLK9860469366</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:58:48 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:42:05 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr"/>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>27.7532644899109, 85.34095673714198 GPS Coordinates Nearest: KAT028-01-3/5-L26 (191m Road) Map: CG D</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>9860469366@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>06:44 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>L26-5</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv related issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>20h 43m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv related issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:19 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>iptv related issue</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352779</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Narayan kumar khatri</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Narayan kumar khatri</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9860469366</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:42:05 AM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>KLK9860469366</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:58:48 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:42:05 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>27.7532644899109, 85.34095673714198 GPS Coordinates Nearest: KAT028-01-3/5-L26 (191m Road) Map: CG D</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>9860469366@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>06:44 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>L26-5</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>20h 43m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:16 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341380</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Aama Milan Kendra</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Aama Milan Kendra</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9851220331</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:25:27 AM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9841863259</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 02:06:54 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:25:27 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>27.6907</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Chakrabarti Habi Education Academy College of Law,Bijulibazar, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr"/>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Rahul Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>L48-6</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>85.32893</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>9d 21h 18m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX10" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:04 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>interent not working</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342441</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Dex Nine pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Dex Nine pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9865995180</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:04:18 AM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>LTP9700022257</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 01:33:16 PM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:04:18 AM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr">
+        <is>
+          <t>Request</t>
+        </is>
+      </c>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>27.646537000000006, 85.31367780674677, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>dexnineco@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>05:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr"/>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>CDB517</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>8d 21h 31m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -1042,7 +1042,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2294,10 +2294,8 @@
           <t>Naresh Acharya</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9842295764</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9842295764</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -2332,10 +2330,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>27.67706</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>27.67706</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -2387,25 +2383,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>1,3</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>85.3458</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>85.3458</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
@@ -2506,10 +2498,8 @@
           <t>Narayan kumar khatri</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9860469366</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9860469366</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2599,10 +2589,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
@@ -2613,7 +2601,7 @@
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv related issue  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2714,10 +2702,8 @@
           <t>Narayan kumar khatri</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9860469366</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9860469366</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2807,10 +2793,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
@@ -2821,7 +2805,7 @@
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
@@ -2922,10 +2906,8 @@
           <t>Aama Milan Kendra</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9851220331</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9851220331</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2960,10 +2942,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>27.6907</t>
-        </is>
+      <c r="Y10" s="3" t="n">
+        <v>27.6907</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
@@ -3015,25 +2995,21 @@
           <t>Rahul Chaudhary</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>L48-6</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>85.32893</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>85.32893</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
@@ -3134,10 +3110,8 @@
           <t>Dex Nine pvt. Ltd.</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9865995180</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9865995180</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -3172,10 +3146,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y11" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
@@ -3231,25 +3203,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>CDB517</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP11" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>0</v>
@@ -832,7 +832,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -973,7 +973,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>2</v>
@@ -982,7 +982,7 @@
         <v>2</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -996,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX11"/>
+  <dimension ref="A1:AX12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1042,7 +1042,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3251,6 +3251,222 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:04 PM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353606</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Shrestha</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Shrestha</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9861804477</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:04:05 PM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>LTP9861804477</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:54:48 AM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:04:05 PM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.666100</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Nhu Pukhu (Rani Pokhari) Marg, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>test@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>02:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>CDB105</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.322084</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>2h 9m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -616,20 +616,38 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>54.5%</t>
+      <c r="B8" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -688,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -723,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
     </row>
@@ -734,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>46.7%</t>
         </is>
       </c>
     </row>
@@ -761,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -770,7 +788,8 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -806,6 +825,11 @@
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
           <t>Grand Total</t>
         </is>
       </c>
@@ -826,13 +850,16 @@
         <v>4</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="6" t="n">
-        <v>5</v>
+      <c r="G2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -856,18 +883,21 @@
       <c r="F3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Audio &amp; Video Syn Issue</t>
+          <t>Download &amp; Upload Speed Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -876,19 +906,22 @@
         <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -906,46 +939,52 @@
       <c r="F5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
@@ -954,35 +993,69 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="D9" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>10</v>
+      <c r="H9" s="4" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -996,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX12"/>
+  <dimension ref="A1:AX16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1025,7 +1098,7 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
@@ -3318,10 +3391,8 @@
           <t>Sudip Shrestha</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9861804477</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9861804477</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -3356,10 +3427,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.666100</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.6661</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -3415,55 +3484,899 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>CDB105</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.322084</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.322084</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>2h 9m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
           <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS12" s="3" t="inlineStr">
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:19 PM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 router upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router upgrade</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352339</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Kamal Shali Ghimire</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Kamal Shali Ghimire</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9851159666</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:19:17 PM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9851159666</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 10:30:19 AM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:19:17 PM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>27.7307</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>Devkota Brothers, P8J9+35H, Samakhushi - Ranibari Rd, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>ghimire_ks@yahoo.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>11:49 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Anu Bogati</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>L16-7</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>85.3175</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 router upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
-          <t>2h 9m</t>
-        </is>
-      </c>
-      <c r="AU12" s="3" t="inlineStr">
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 48m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV12" s="3" t="inlineStr">
-        <is>
-          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="AW12" s="3" t="inlineStr">
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6 router upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:26 PM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow Internet  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>slow Internet</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348195</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Anuj  Kuwar</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Anuj  Kuwar</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9860614634</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:26:25 PM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9860614634</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 11:21:12 AM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:26:25 PM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr"/>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Clicked Location 27.70858, 85.33194 Nearest: CDB436 (45m Road) Map: CG Putalisadak, Bagmati, Nepal,</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr"/>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Download &amp; Upload Speed Issue</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>08:26 hour</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>CDB256</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr"/>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow Internet  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>4d 1h 5m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow Internet  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX12" s="3" t="inlineStr">
-        <is>
-          <t>Rajesh Maharjan</t>
+      <c r="AX14" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:28 PM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352921</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Babu Amgain</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Babu Amgain</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9851067572</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:29:35 PM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>9851067572</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:29:35 PM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:28:17 PM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>27.727574</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>Corona school, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr"/>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>05:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>CDB264</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>85.291697</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>19h 58m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>19h 58m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX15" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:27 PM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352921</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Babu Amgain</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Suresh Babu Amgain</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9851067572</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:29:35 PM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9851067572</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:29:35 PM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:28:17 PM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>27.727574</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Corona school, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr"/>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>05:58 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>CDB264</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>85.291697</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>19h 58m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>19h 58m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -1115,7 +1115,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3599,10 +3599,8 @@
           <t>Kamal Shali Ghimire</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9851159666</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9851159666</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3637,10 +3635,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y13" s="3" t="inlineStr">
-        <is>
-          <t>27.7307</t>
-        </is>
+      <c r="Y13" s="3" t="n">
+        <v>27.7307</v>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
@@ -3696,25 +3692,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>L16-7</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>85.3175</t>
-        </is>
+      <c r="AP13" s="3" t="n">
+        <v>85.3175</v>
       </c>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>Case :  wifi 6 router upgrade  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
@@ -3815,10 +3807,8 @@
           <t>Anuj  Kuwar</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9860614634</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9860614634</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3886,10 +3876,8 @@
           <t>Download &amp; Upload Speed Issue</t>
         </is>
       </c>
-      <c r="AH14" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH14" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI14" s="3" t="inlineStr">
         <is>
@@ -3908,10 +3896,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
@@ -3922,7 +3908,7 @@
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : slow Internet  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
@@ -4023,10 +4009,8 @@
           <t>Suresh Babu Amgain</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9851067572</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9851067572</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -4061,10 +4045,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t>27.727574</t>
-        </is>
+      <c r="Y15" s="3" t="n">
+        <v>27.727574</v>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
@@ -4116,25 +4098,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
           <t>CDB264</t>
         </is>
       </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>85.291697</t>
-        </is>
+      <c r="AP15" s="3" t="n">
+        <v>85.291697</v>
       </c>
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
@@ -4235,10 +4213,8 @@
           <t>Suresh Babu Amgain</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9851067572</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9851067572</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -4273,10 +4249,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t>27.727574</t>
-        </is>
+      <c r="Y16" s="3" t="n">
+        <v>27.727574</v>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
@@ -4328,25 +4302,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>CDB264</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>85.291697</t>
-        </is>
+      <c r="AP16" s="3" t="n">
+        <v>85.291697</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.6%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>29.4%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>11.8%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>52.9%</t>
         </is>
       </c>
     </row>
@@ -847,10 +847,10 @@
         <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>1</v>
@@ -859,7 +859,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -1043,10 +1043,10 @@
         <v>1</v>
       </c>
       <c r="D9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>4</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>2</v>
@@ -1055,7 +1055,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX16"/>
+  <dimension ref="A1:AX18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1103,7 +1103,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="23" customWidth="1" min="32" max="32"/>
+    <col width="25" customWidth="1" min="32" max="32"/>
     <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -1115,7 +1115,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -4350,6 +4350,426 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:49 PM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351456</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Puja Regmi</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Puja Regmi</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9843038600</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:49:05 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>9843038600</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:48:59 PM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:49:05 PM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr"/>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Swimming Pool Marg Lalitpur 44700, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr"/>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>19:01 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Puja Khadka</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>1,12</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr"/>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX17" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 1:02 PM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352734</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Rupak Subedi</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Rupak Subedi</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9851175712</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:02:33 PM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>9851175712</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:34:05 PM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:02:33 PM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>27.756192</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Q822+54F way Tarakeshwar 44600,Near Sunflower Academy (English Medium SS) , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>subedirupak8@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>08:28 hour</t>
+        </is>
+      </c>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>L5-1</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>85.29951</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>22h 28m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX18" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>68.4%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>31.6%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>15.8%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>47.4%</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>2</v>
@@ -859,7 +859,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -1043,7 +1043,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>4</v>
@@ -1055,7 +1055,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX18"/>
+  <dimension ref="A1:AX20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1103,7 +1103,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="25" customWidth="1" min="32" max="32"/>
+    <col width="28" customWidth="1" min="32" max="32"/>
     <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -4417,10 +4417,8 @@
           <t>Puja Regmi</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9843038600</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9843038600</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -4506,10 +4504,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
@@ -4520,7 +4516,7 @@
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
@@ -4621,10 +4617,8 @@
           <t>Rupak Subedi</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9851175712</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9851175712</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -4659,10 +4653,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t>27.756192</t>
-        </is>
+      <c r="Y18" s="3" t="n">
+        <v>27.756192</v>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
@@ -4718,55 +4710,479 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
           <t>L5-1</t>
         </is>
       </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>85.29951</t>
-        </is>
+      <c r="AP18" s="3" t="n">
+        <v>85.29951</v>
       </c>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>22h 28m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
           <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS18" s="3" t="inlineStr">
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX18" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 1:03 PM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : router uprade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>router uprade</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353630</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Ranjana Yadav</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Ranjana Yadav</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9819622436</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:03:40 PM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>9844495200</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 10:10:10 AM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:03:40 PM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>27.656123</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>Mahalaxmi municipality baghmati Nepal , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>yadavranjana099@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr"/>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>CDB025</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>85.339142</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : router uprade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT18" s="3" t="inlineStr">
-        <is>
-          <t>22h 28m</t>
-        </is>
-      </c>
-      <c r="AU18" s="3" t="inlineStr">
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>2h 53m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : router uprade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 1:08 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>IPTV ISSUE</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352510</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Barjachrya</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Barjachrya</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9841255601</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:08:32 PM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>CHB9841255601</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:05:06 PM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:08:32 PM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>Lazimpat, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh@gamil.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>11:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Bishwojeet Adhikari</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>CDB328</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 3m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV18" s="3" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW18" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
-        </is>
-      </c>
-      <c r="AX18" s="3" t="inlineStr">
-        <is>
-          <t>Sanjeev Giri</t>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX20" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>35.0%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>15.0%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>45.0%</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -865,7 +865,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Download &amp; Upload Speed Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -893,11 +893,11 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Download &amp; Upload Speed Issue</t>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -906,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
@@ -921,11 +921,11 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Audio &amp; Video Syn Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -934,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -1005,7 +1005,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -1031,31 +1031,59 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B10" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E10" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" s="4" t="n">
+      <c r="F10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="4" t="n">
-        <v>16</v>
+      <c r="H10" s="4" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1069,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX20"/>
+  <dimension ref="A1:AX21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4825,10 +4853,8 @@
           <t>Ranjana Yadav</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9819622436</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9819622436</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4863,10 +4889,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y19" s="3" t="inlineStr">
-        <is>
-          <t>27.656123</t>
-        </is>
+      <c r="Y19" s="3" t="n">
+        <v>27.656123</v>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
@@ -4918,25 +4942,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
           <t>CDB025</t>
         </is>
       </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>85.339142</t>
-        </is>
+      <c r="AP19" s="3" t="n">
+        <v>85.339142</v>
       </c>
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>Case : router uprade   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
@@ -5027,20 +5047,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M20" s="3" t="inlineStr"/>
       <c r="N20" s="3" t="inlineStr">
         <is>
           <t>Rajesh Barjachrya</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9841255601</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9841255601</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -5075,10 +5089,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y20" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y20" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
@@ -5134,55 +5146,267 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
           <t>CDB328</t>
         </is>
       </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP20" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 3m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
           <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS20" s="3" t="inlineStr">
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX20" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 1:27 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>slow internet</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352942</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Unish Dulal</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Unish Dulal</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9803282720</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:27:30 PM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>9803282720</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:37:44 PM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:27:30 PM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr">
+        <is>
+          <t>Box End</t>
+        </is>
+      </c>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>BhaktapurKaushaltaarTersetaar, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>dunish550@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>06:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr"/>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>2,2</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT20" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 3m</t>
-        </is>
-      </c>
-      <c r="AU20" s="3" t="inlineStr">
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>20h 49m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV20" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV ISSUE  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="AW20" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
-        </is>
-      </c>
-      <c r="AX20" s="3" t="inlineStr">
-        <is>
-          <t>Ajit Shrestha</t>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -1143,7 +1143,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -5261,10 +5261,8 @@
           <t>Unish Dulal</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9803282720</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9803282720</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -5299,10 +5297,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y21" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
@@ -5358,25 +5354,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>2,2</t>
         </is>
       </c>
-      <c r="AP21" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case : slow internet  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>65.4%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>11.5%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
     </row>
@@ -841,25 +841,25 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -1065,25 +1065,25 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E10" s="4" t="n">
         <v>4</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX21"/>
+  <dimension ref="A1:AX27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1143,7 +1143,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -5402,6 +5402,1274 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 1:57 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353222</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Mohit Shrestha</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Mohit Shrestha</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9813626257</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 07:48:59 PM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9813626257</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 07:48:59 PM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:57:46 PM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t>27.71686</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>P883+P4V Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr"/>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>04:09 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>CDB478</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>85.3028</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>18h 8m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>18h 8m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX22" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 1:55 PM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353527</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Elina Maharjan</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Elina Maharjan</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9802206622</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:55:44 PM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>9802206622</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 08:59:56 AM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:55:44 PM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>27.68315</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>Kupondole Hotel Kutumba, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>maharjanelina05@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr"/>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>3,12</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr">
+        <is>
+          <t>85.31638</t>
+        </is>
+      </c>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>4h 55m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX23" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 1:50 PM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353546</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>som Bahadur thing</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>som Bahadur thing</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9851211866</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:50:39 PM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>LTP9851211866</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:21:53 AM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:50:39 PM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr"/>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>Prime Colony Society - Housing society M8H3+8J9 Naya Bato Lalitpur 44600, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr">
+        <is>
+          <t>9851211866@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>03:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>3,5</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr"/>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>4h 28m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX24" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 2:03 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344890</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Bijay Timilsina</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Bijay Timilsina</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9851326768</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 08:51:26 PM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>9866486431</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 02:16:43 PM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 02:03:01 PM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>27.679234</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Near Chokha Binayak Sthan, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>timilsinakrish@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr"/>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>L16-1</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>85.444639</t>
+        </is>
+      </c>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>17h 11m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>6d 23h 46m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX25" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 2:01 PM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353055</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>BISHNU HARI SHRESTHA</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>BISHNU HARI SHRESTHA</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9708478044</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 05:32:41 PM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>9849426510</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 05:32:41 PM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 02:01:11 PM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t>27.682799</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>Holy garden school, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr"/>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr"/>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>L38-7</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>85.389388</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>20h 28m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>20h 28m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX26" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 1:58 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>slow issue</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352969</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Naresh Acharya</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Naresh Acharya</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9842295764</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:58:17 PM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>9823137550</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:49:39 PM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:58:17 PM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t>27.67706</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>Koteshwor,Shatya Sai baba Marg,House nu -46,Near Suprim Overseas Pvt Ltd,and Khaja Ghar, At Bindabas</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr">
+        <is>
+          <t>acnares2@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr">
+        <is>
+          <t>07:09 hour</t>
+        </is>
+      </c>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr">
+        <is>
+          <t>85.3458</t>
+        </is>
+      </c>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>21h 8m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX27" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>17</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>63.0%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>29.6%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>14.8%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>51.9%</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Download &amp; Upload Speed Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -881,13 +881,13 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -921,7 +921,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Download &amp; Upload Speed Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -1077,13 +1077,13 @@
         <v>4</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX27"/>
+  <dimension ref="A1:AX28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5469,10 +5469,8 @@
           <t>Mohit Shrestha</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9813626257</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9813626257</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -5507,10 +5505,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t>27.71686</t>
-        </is>
+      <c r="Y22" s="3" t="n">
+        <v>27.71686</v>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
@@ -5562,25 +5558,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
           <t>CDB478</t>
         </is>
       </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>85.3028</t>
-        </is>
+      <c r="AP22" s="3" t="n">
+        <v>85.3028</v>
       </c>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
@@ -5681,10 +5673,8 @@
           <t>Elina Maharjan</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9802206622</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9802206622</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -5719,10 +5709,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y23" s="3" t="inlineStr">
-        <is>
-          <t>27.68315</t>
-        </is>
+      <c r="Y23" s="3" t="n">
+        <v>27.68315</v>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
@@ -5774,25 +5762,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
           <t>3,12</t>
         </is>
       </c>
-      <c r="AP23" s="3" t="inlineStr">
-        <is>
-          <t>85.31638</t>
-        </is>
+      <c r="AP23" s="3" t="n">
+        <v>85.31638</v>
       </c>
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
@@ -5893,10 +5877,8 @@
           <t>som Bahadur thing</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9851211866</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9851211866</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -5986,10 +5968,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
@@ -6000,7 +5980,7 @@
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
@@ -6101,10 +6081,8 @@
           <t>Bijay Timilsina</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9851326768</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9851326768</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -6139,10 +6117,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t>27.679234</t>
-        </is>
+      <c r="Y25" s="3" t="n">
+        <v>27.679234</v>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
@@ -6194,25 +6170,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
           <t>L16-1</t>
         </is>
       </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>85.444639</t>
-        </is>
+      <c r="AP25" s="3" t="n">
+        <v>85.444639</v>
       </c>
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
@@ -6313,10 +6285,8 @@
           <t>BISHNU HARI SHRESTHA</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9708478044</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9708478044</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -6351,10 +6321,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t>27.682799</t>
-        </is>
+      <c r="Y26" s="3" t="n">
+        <v>27.682799</v>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
@@ -6402,25 +6370,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
           <t>L38-7</t>
         </is>
       </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>85.389388</t>
-        </is>
+      <c r="AP26" s="3" t="n">
+        <v>85.389388</v>
       </c>
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
@@ -6521,10 +6485,8 @@
           <t>Naresh Acharya</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9842295764</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9842295764</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -6559,10 +6521,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y27" s="3" t="inlineStr">
-        <is>
-          <t>27.67706</t>
-        </is>
+      <c r="Y27" s="3" t="n">
+        <v>27.67706</v>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
@@ -6618,53 +6578,261 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
           <t>1,3</t>
         </is>
       </c>
-      <c r="AP27" s="3" t="inlineStr">
-        <is>
-          <t>85.3458</t>
-        </is>
+      <c r="AP27" s="3" t="n">
+        <v>85.3458</v>
       </c>
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>21h 8m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
           <t>Case : slow issue   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS27" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT27" s="3" t="inlineStr">
-        <is>
-          <t>21h 8m</t>
-        </is>
-      </c>
-      <c r="AU27" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV27" s="3" t="inlineStr">
-        <is>
-          <t>Case : slow issue   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW27" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
       <c r="AX27" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 2:07 PM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>IPTV issue</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353054</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Umesh Thakur</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Umesh Thakur</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>9805889944</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 08:41:08 AM</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>BKT9805889944</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 05:32:23 PM</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 02:07:15 PM</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr">
+        <is>
+          <t>27.659463</t>
+        </is>
+      </c>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr">
+        <is>
+          <t>Changathali, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF28" s="3" t="inlineStr">
+        <is>
+          <t>test@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG28" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr"/>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr">
+        <is>
+          <t>Naman Mallik</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>2,10</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr">
+        <is>
+          <t>85.359684</t>
+        </is>
+      </c>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>5h 26m</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>20h 34m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX28" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -622,10 +622,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>64.5%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>29.0%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.1%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>51.6%</t>
         </is>
       </c>
     </row>
@@ -779,10 +779,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -847,19 +847,19 @@
         <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -893,11 +893,11 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Audio &amp; Video Syn Issue</t>
+          <t>Download &amp; Upload Speed Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -906,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
@@ -921,11 +921,11 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Download &amp; Upload Speed Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -934,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -1005,7 +1005,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>1</v>
@@ -1033,7 +1033,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -1059,31 +1059,59 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>23</v>
+      <c r="D11" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX28"/>
+  <dimension ref="A1:AX32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1110,10 +1138,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -1132,7 +1160,7 @@
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="28" customWidth="1" min="32" max="32"/>
-    <col width="32" customWidth="1" min="33" max="33"/>
+    <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -6683,20 +6711,14 @@
           <t>On Hold</t>
         </is>
       </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M28" s="3" t="inlineStr"/>
       <c r="N28" s="3" t="inlineStr">
         <is>
           <t>Umesh Thakur</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>9805889944</t>
-        </is>
+      <c r="O28" s="3" t="n">
+        <v>9805889944</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
@@ -6731,10 +6753,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y28" s="3" t="inlineStr">
-        <is>
-          <t>27.659463</t>
-        </is>
+      <c r="Y28" s="3" t="n">
+        <v>27.659463</v>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
@@ -6786,55 +6806,891 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN28" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
           <t>2,10</t>
         </is>
       </c>
-      <c r="AP28" s="3" t="inlineStr">
-        <is>
-          <t>85.359684</t>
-        </is>
+      <c r="AP28" s="3" t="n">
+        <v>85.359684</v>
       </c>
       <c r="AQ28" s="3" t="inlineStr"/>
       <c r="AR28" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>5h 26m</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>20h 34m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
           <t>Case : IPTV issue  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS28" s="3" t="inlineStr">
-        <is>
-          <t>5h 26m</t>
-        </is>
-      </c>
-      <c r="AT28" s="3" t="inlineStr">
-        <is>
-          <t>20h 34m</t>
-        </is>
-      </c>
-      <c r="AU28" s="3" t="inlineStr">
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX28" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 2:29 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353804</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>bindu bhattrai</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>bindu bhattrai</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9841881780</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:46:37 AM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>9841881780</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:46:37 AM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 02:29:08 PM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr"/>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>balkot, shanti chock, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr"/>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr"/>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>L53-8</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr"/>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>2h 42m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>2h 42m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
         <is>
           <t>Other / In Progress (On Hold)</t>
         </is>
       </c>
-      <c r="AV28" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV issue  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW28" s="3" t="inlineStr">
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX29" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 2:24 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1344823</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Saroj Man Shrestha</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Saroj Man Shrestha</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9843807409</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 02:24:28 PM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>9849669368</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>24 Sep 2026 01:20:51 PM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 02:24:28 PM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr">
+        <is>
+          <t>27.67556</t>
+        </is>
+      </c>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>Khachhen, 16, Shakyai Unique emporium nearby, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr">
+        <is>
+          <t>sarojmansh@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr">
+        <is>
+          <t>13:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr">
+        <is>
+          <t>85.32319</t>
+        </is>
+      </c>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>7d 1h 3m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX30" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 2:26 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353539</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Chakra prasad thapa magar</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Chakra prasad thapa magar</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>9821507017</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 02:26:57 PM</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>9851122942</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:13:51 AM</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 02:26:57 PM</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr"/>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>Near Lumbini Gas, P8P7+G4P, Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr">
+        <is>
+          <t>sajinthapa98@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr">
+        <is>
+          <t>04:26 hour</t>
+        </is>
+      </c>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>L46-5</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr"/>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>5h 13m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX31" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 2:22 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>IPTV ISSUE</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352583</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Cyrus Shrestha</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Cyrus Shrestha</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9861926855</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 03:15:03 PM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>DRZ9861926855</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 12:49:09 PM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 02:22:49 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>27.70284</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>Kalimati 27.7027679, 85.2861990 - Near Jehovah's Witnesses Society,Kalimati,Kathmandu - Kathmandu Me</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr">
+        <is>
+          <t>5sos.cyrus@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>11:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>Prajwal Adhikari</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>2,2</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>85.2862</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>23h 7m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 33m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV ISSUE  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
         </is>
       </c>
-      <c r="AX28" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
+      <c r="AX32" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -1171,7 +1171,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -6921,10 +6921,8 @@
           <t>bindu bhattrai</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9841881780</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9841881780</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -7006,10 +7004,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
@@ -7020,7 +7016,7 @@
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
@@ -7121,10 +7117,8 @@
           <t>Saroj Man Shrestha</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9843807409</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9843807409</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -7159,10 +7153,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y30" s="3" t="inlineStr">
-        <is>
-          <t>27.67556</t>
-        </is>
+      <c r="Y30" s="3" t="n">
+        <v>27.67556</v>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
@@ -7218,25 +7210,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="AP30" s="3" t="inlineStr">
-        <is>
-          <t>85.32319</t>
-        </is>
+      <c r="AP30" s="3" t="n">
+        <v>85.32319</v>
       </c>
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
@@ -7337,10 +7325,8 @@
           <t>Chakra prasad thapa magar</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>9821507017</t>
-        </is>
+      <c r="O31" s="3" t="n">
+        <v>9821507017</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
@@ -7430,10 +7416,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN31" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
@@ -7444,7 +7428,7 @@
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
@@ -7545,10 +7529,8 @@
           <t>Cyrus Shrestha</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9861926855</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9861926855</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -7583,10 +7565,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t>27.70284</t>
-        </is>
+      <c r="Y32" s="3" t="n">
+        <v>27.70284</v>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
@@ -7642,25 +7622,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
           <t>2,2</t>
         </is>
       </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>85.2862</t>
-        </is>
+      <c r="AP32" s="3" t="n">
+        <v>85.28619999999999</v>
       </c>
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV ISSUE  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>15.2%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>48.5%</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -850,7 +850,7 @@
         <v>9</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>4</v>
@@ -859,7 +859,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -921,7 +921,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -949,20 +949,20 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Audio &amp; Video Syn Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
@@ -977,20 +977,20 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -1005,7 +1005,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Channel buffering,feeze issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -1033,7 +1033,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>1</v>
@@ -1061,7 +1061,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -1087,31 +1087,59 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B12" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D12" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E11" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="F11" s="4" t="n">
+      <c r="E12" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="G11" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>27</v>
+      <c r="G12" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1125,7 +1153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX32"/>
+  <dimension ref="A1:AX34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1171,7 +1199,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -7670,6 +7698,422 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 3:01 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>slow issue</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353679</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Lamichhane</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Lamichhane</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>9849952080</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:01:53 PM</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>9849952080</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 10:38:04 AM</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:01:53 PM</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr"/>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>loktanrik chowk Hile tole, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr"/>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>04:23 hour</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>Subash Sunuwar</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>L30-4</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr"/>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>4h 23m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX33" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 2:53 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : CONFINGURE ISSUE  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>CONFINGURE ISSUE</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353468</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Bigyan Shrestha</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Bigyan Shrestha</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9746458564</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 10:18:34 AM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>9813031745</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 07:30:42 AM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 02:53:21 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t>27.68067</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu Matatirtha Mahalaxmi school, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>stha.bigyan03@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr"/>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Sanam Sadar</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>CDB348</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr">
+        <is>
+          <t>85.23175</t>
+        </is>
+      </c>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : CONFINGURE ISSUE  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>4h 34m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>7h 22m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : CONFINGURE ISSUE  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX34" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -706,14 +706,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>13.9%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -847,19 +847,19 @@
         <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>4</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -1127,19 +1127,19 @@
         <v>1</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>6</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>3</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1153,7 +1153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX34"/>
+  <dimension ref="A1:AX37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1166,10 +1166,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -1187,7 +1187,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="28" customWidth="1" min="32" max="32"/>
+    <col width="29" customWidth="1" min="32" max="32"/>
     <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -7755,20 +7755,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M33" s="3" t="inlineStr"/>
       <c r="N33" s="3" t="inlineStr">
         <is>
           <t>Susmita Lamichhane</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>9849952080</t>
-        </is>
+      <c r="O33" s="3" t="n">
+        <v>9849952080</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
@@ -7854,10 +7848,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN33" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
@@ -7868,7 +7860,7 @@
       <c r="AQ33" s="3" t="inlineStr"/>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
@@ -7969,10 +7961,8 @@
           <t>Bigyan Shrestha</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9746458564</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9746458564</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -8007,10 +7997,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y34" s="3" t="inlineStr">
-        <is>
-          <t>27.68067</t>
-        </is>
+      <c r="Y34" s="3" t="n">
+        <v>27.68067</v>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
@@ -8062,47 +8050,43 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
           <t>CDB348</t>
         </is>
       </c>
-      <c r="AP34" s="3" t="inlineStr">
-        <is>
-          <t>85.23175</t>
-        </is>
+      <c r="AP34" s="3" t="n">
+        <v>85.23175000000001</v>
       </c>
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>4h 34m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>7h 22m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
           <t>Case : CONFINGURE ISSUE  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS34" s="3" t="inlineStr">
-        <is>
-          <t>4h 34m</t>
-        </is>
-      </c>
-      <c r="AT34" s="3" t="inlineStr">
-        <is>
-          <t>7h 22m</t>
-        </is>
-      </c>
-      <c r="AU34" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV34" s="3" t="inlineStr">
-        <is>
-          <t>Case : CONFINGURE ISSUE  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW34" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -8111,6 +8095,646 @@
       <c r="AX34" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 3:13 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>TKT1346370</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Kumari Nanda Jaiswar Bhatta</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>Kumari Nanda Jaiswar Bhatta</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>9818548099</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:13:22 PM</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>9867369591</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 04:48:50 PM</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:13:22 PM</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t>27.68548</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC35" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>Madhya Marg, Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr">
+        <is>
+          <t>anshusafalpatel@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG35" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr">
+        <is>
+          <t>00:25 hour</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>Puja Khadka</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>CDB488</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>85.33084</t>
+        </is>
+      </c>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>5d 22h 24m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX35" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 3:03 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353556</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Umesh Thakurathi</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Umesh Thakurathi</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9841372017</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:03:29 PM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>9805782711</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:27:16 AM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:03:30 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr"/>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>Suvakamana Gate, RadheRadhe Bhawan, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>suren@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr">
+        <is>
+          <t>05:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>3,10</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr"/>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>5h 36m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX36" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 3:02 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353885</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh Bhandari</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh Bhandari</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9863635254</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:02:38 PM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>9863635254</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:42:19 PM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:02:38 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr">
+        <is>
+          <t>27.668862</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>3 Sundar Nagr Marg Balkot Bhaktapur Near By Rose Village., Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
+        <is>
+          <t>eramesh.bhandari@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr">
+        <is>
+          <t>02:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>L4-7</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>85.374149</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>2h 20m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX37" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.6%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>32.4%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.5%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.4%</t>
         </is>
       </c>
     </row>
@@ -856,10 +856,10 @@
         <v>6</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -1136,10 +1136,10 @@
         <v>9</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1153,7 +1153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX37"/>
+  <dimension ref="A1:AX38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8165,10 +8165,8 @@
           <t>Kumari Nanda Jaiswar Bhatta</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>9818548099</t>
-        </is>
+      <c r="O35" s="3" t="n">
+        <v>9818548099</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
@@ -8203,10 +8201,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y35" s="3" t="inlineStr">
-        <is>
-          <t>27.68548</t>
-        </is>
+      <c r="Y35" s="3" t="n">
+        <v>27.68548</v>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
@@ -8262,25 +8258,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN35" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
           <t>CDB488</t>
         </is>
       </c>
-      <c r="AP35" s="3" t="inlineStr">
-        <is>
-          <t>85.33084</t>
-        </is>
+      <c r="AP35" s="3" t="n">
+        <v>85.33083999999999</v>
       </c>
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
@@ -8381,10 +8373,8 @@
           <t>Umesh Thakurathi</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9841372017</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9841372017</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -8474,10 +8464,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
@@ -8488,7 +8476,7 @@
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>Case : Wi-Fi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
@@ -8589,10 +8577,8 @@
           <t>Ramesh Bhandari</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9863635254</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9863635254</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -8627,10 +8613,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y37" s="3" t="inlineStr">
-        <is>
-          <t>27.668862</t>
-        </is>
+      <c r="Y37" s="3" t="n">
+        <v>27.668862</v>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
@@ -8686,47 +8670,43 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
           <t>L4-7</t>
         </is>
       </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>85.374149</t>
-        </is>
+      <c r="AP37" s="3" t="n">
+        <v>85.374149</v>
       </c>
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>2h 20m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS37" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT37" s="3" t="inlineStr">
-        <is>
-          <t>2h 20m</t>
-        </is>
-      </c>
-      <c r="AU37" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV37" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW37" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -8735,6 +8715,222 @@
       <c r="AX37" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 3:30 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353585</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Sunaina Maharjan</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Sunaina Maharjan</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>9862794549</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:45:05 AM</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>9880955162</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:45:05 AM</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:30:54 PM</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC38" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu Balambu Gurjudhara, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr">
+        <is>
+          <t>sunayanamah33@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr">
+        <is>
+          <t>05:30 hour</t>
+        </is>
+      </c>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>CDB052</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>5h 45m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>5h 45m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX38" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>68.4%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>34.2%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.2%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -949,20 +949,20 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
@@ -977,20 +977,20 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -1005,11 +1005,11 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Query For Secondary Router /Repeater</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>0</v>
@@ -1024,7 +1024,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="6" t="n">
         <v>1</v>
@@ -1033,7 +1033,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Channel buffering,feeze issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -1061,7 +1061,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -1077,10 +1077,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>1</v>
@@ -1089,7 +1089,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
@@ -1115,31 +1115,59 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C12" s="4" t="n">
+      <c r="B13" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D13" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E13" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H12" s="4" t="n">
-        <v>33</v>
+      <c r="H13" s="4" t="n">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1153,7 +1181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX38"/>
+  <dimension ref="A1:AX39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1164,7 +1192,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -1187,7 +1215,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="29" customWidth="1" min="32" max="32"/>
+    <col width="39" customWidth="1" min="32" max="32"/>
     <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -8785,10 +8813,8 @@
           <t>Sunaina Maharjan</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>9862794549</t>
-        </is>
+      <c r="O38" s="3" t="n">
+        <v>9862794549</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
@@ -8823,10 +8849,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y38" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y38" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
@@ -8882,47 +8906,43 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN38" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
           <t>CDB052</t>
         </is>
       </c>
-      <c r="AP38" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP38" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ38" s="3" t="inlineStr"/>
       <c r="AR38" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>5h 45m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>5h 45m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS38" s="3" t="inlineStr">
-        <is>
-          <t>5h 45m</t>
-        </is>
-      </c>
-      <c r="AT38" s="3" t="inlineStr">
-        <is>
-          <t>5h 45m</t>
-        </is>
-      </c>
-      <c r="AU38" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV38" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW38" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -8931,6 +8951,222 @@
       <c r="AX38" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 3:43 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : secondary router connection  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>secondary router connection</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352458</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Mohsin Ansari</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>Mohsin Ansari</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>9849565480</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:43:31 PM</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>CHB9849565489</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 11:31:10 AM</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:43:31 PM</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA39" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC39" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr">
+        <is>
+          <t>27.69766201137519, 85.30675643311395 GPS Coordinates Nearest: KAT008-01-2/11-ADB005 (0m Road) Map: C</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr">
+        <is>
+          <t>amohsin20@britishmodelcollege.edu.np</t>
+        </is>
+      </c>
+      <c r="AG39" s="3" t="inlineStr">
+        <is>
+          <t>Query For Secondary Router /Repeater</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr">
+        <is>
+          <t>14:12 hour</t>
+        </is>
+      </c>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t>Prajwal Adhikari</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>CDB327</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>Case : secondary router connection  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 12m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : secondary router connection  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX39" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>32.5%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.5%</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>4</v>
@@ -859,7 +859,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -1155,7 +1155,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>6</v>
@@ -1167,7 +1167,7 @@
         <v>4</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1181,7 +1181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX39"/>
+  <dimension ref="A1:AX41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -9021,10 +9021,8 @@
           <t>Mohsin Ansari</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>9849565480</t>
-        </is>
+      <c r="O39" s="3" t="n">
+        <v>9849565480</v>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
@@ -9059,10 +9057,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y39" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y39" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
@@ -9118,55 +9114,479 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN39" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
           <t>CDB327</t>
         </is>
       </c>
-      <c r="AP39" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP39" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ39" s="3" t="inlineStr"/>
       <c r="AR39" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 12m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
           <t>Case : secondary router connection  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS39" s="3" t="inlineStr">
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX39" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 3:53 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353930</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Rekha Rana</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Rekha Rana</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>9815651617</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:53:28 PM</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>9851651617</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 01:09:35 PM</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:53:28 PM</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr">
+        <is>
+          <t>27.694877</t>
+        </is>
+      </c>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA40" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB40" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC40" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr">
+        <is>
+          <t>Near  to Milan Chowk,Kathmandu , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF40" s="3" t="inlineStr">
+        <is>
+          <t>ranarekha504@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="3" t="inlineStr">
+        <is>
+          <t>02:44 hour</t>
+        </is>
+      </c>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO40" s="3" t="inlineStr">
+        <is>
+          <t>L30-3</t>
+        </is>
+      </c>
+      <c r="AP40" s="3" t="inlineStr">
+        <is>
+          <t>85.342056</t>
+        </is>
+      </c>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT39" s="3" t="inlineStr">
-        <is>
-          <t>1d 4h 12m</t>
-        </is>
-      </c>
-      <c r="AU39" s="3" t="inlineStr">
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>2h 43m</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV39" s="3" t="inlineStr">
-        <is>
-          <t>Case : secondary router connection  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
-      <c r="AW39" s="3" t="inlineStr">
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX40" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 3:55 PM</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353055</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>BISHNU HARI SHRESTHA</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>BISHNU HARI SHRESTHA</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>9708478044</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX39" s="3" t="inlineStr">
-        <is>
-          <t>Ajit Shrestha</t>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:55:19 PM</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>9849426510</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 05:32:41 PM</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:55:19 PM</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t>27.682799</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA41" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB41" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC41" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD41" s="3" t="inlineStr"/>
+      <c r="AE41" s="3" t="inlineStr">
+        <is>
+          <t>Holy garden school, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF41" s="3" t="inlineStr"/>
+      <c r="AG41" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="inlineStr"/>
+      <c r="AI41" s="3" t="inlineStr">
+        <is>
+          <t>08:23 hour</t>
+        </is>
+      </c>
+      <c r="AJ41" s="3" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>L38-7</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>85.389388</t>
+        </is>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr"/>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>22h 22m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX41" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>6</v>
-      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>70.7%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>34.1%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.2%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>51.2%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
         <v>11</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>6</v>
@@ -859,7 +859,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -1158,7 +1158,7 @@
         <v>11</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>9</v>
@@ -1167,7 +1167,7 @@
         <v>4</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1181,7 +1181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX41"/>
+  <dimension ref="A1:AX42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -9229,10 +9229,8 @@
           <t>Rekha Rana</t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>9815651617</t>
-        </is>
+      <c r="O40" s="3" t="n">
+        <v>9815651617</v>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
@@ -9267,10 +9265,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y40" s="3" t="inlineStr">
-        <is>
-          <t>27.694877</t>
-        </is>
+      <c r="Y40" s="3" t="n">
+        <v>27.694877</v>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
@@ -9326,25 +9322,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN40" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
           <t>L30-3</t>
         </is>
       </c>
-      <c r="AP40" s="3" t="inlineStr">
-        <is>
-          <t>85.342056</t>
-        </is>
+      <c r="AP40" s="3" t="n">
+        <v>85.342056</v>
       </c>
       <c r="AQ40" s="3" t="inlineStr"/>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
@@ -9445,10 +9437,8 @@
           <t>BISHNU HARI SHRESTHA</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>9708478044</t>
-        </is>
+      <c r="O41" s="3" t="n">
+        <v>9708478044</v>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
@@ -9483,10 +9473,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y41" s="3" t="inlineStr">
-        <is>
-          <t>27.682799</t>
-        </is>
+      <c r="Y41" s="3" t="n">
+        <v>27.682799</v>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
@@ -9538,55 +9526,267 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN41" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
           <t>L38-7</t>
         </is>
       </c>
-      <c r="AP41" s="3" t="inlineStr">
-        <is>
-          <t>85.389388</t>
-        </is>
+      <c r="AP41" s="3" t="n">
+        <v>85.389388</v>
       </c>
       <c r="AQ41" s="3" t="inlineStr"/>
       <c r="AR41" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>22h 22m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS41" s="3" t="inlineStr">
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX41" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 4:06 PM</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : 6G router setup request  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>6G router setup request</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353605</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Saroj Adhikari</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Saroj Adhikari</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>9860589232</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:06:04 PM</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>9860589232</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:54:39 AM</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:06:04 PM</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr">
+        <is>
+          <t>27.744763</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC42" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr">
+        <is>
+          <t>Request</t>
+        </is>
+      </c>
+      <c r="AE42" s="3" t="inlineStr">
+        <is>
+          <t>Nepal Model School, à¤¶à¥à¤°à¥€à¤Ÿà¥‹à¤², Tokha 44600, 27.74397, 85.33182, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF42" s="3" t="inlineStr">
+        <is>
+          <t>a.saroj463@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG42" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="inlineStr"/>
+      <c r="AI42" s="3" t="inlineStr">
+        <is>
+          <t>06:06 hour</t>
+        </is>
+      </c>
+      <c r="AJ42" s="3" t="inlineStr"/>
+      <c r="AK42" s="3" t="inlineStr"/>
+      <c r="AL42" s="3" t="inlineStr"/>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>L2-3</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr">
+        <is>
+          <t>85.335609</t>
+        </is>
+      </c>
+      <c r="AQ42" s="3" t="inlineStr"/>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>Case : 6G router setup request  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT41" s="3" t="inlineStr">
-        <is>
-          <t>22h 22m</t>
-        </is>
-      </c>
-      <c r="AU41" s="3" t="inlineStr">
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>6h 11m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV41" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW41" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
-        </is>
-      </c>
-      <c r="AX41" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>Case : 6G router setup request  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX42" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>7</v>
-      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>1</v>
@@ -887,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1158,7 +1158,7 @@
         <v>11</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>9</v>
@@ -1167,7 +1167,7 @@
         <v>4</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1181,7 +1181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX42"/>
+  <dimension ref="A1:AX43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1221,7 +1221,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="22" customWidth="1" min="38" max="38"/>
+    <col width="28" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -9641,10 +9641,8 @@
           <t>Saroj Adhikari</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>9860589232</t>
-        </is>
+      <c r="O42" s="3" t="n">
+        <v>9860589232</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
@@ -9679,10 +9677,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y42" s="3" t="inlineStr">
-        <is>
-          <t>27.744763</t>
-        </is>
+      <c r="Y42" s="3" t="n">
+        <v>27.744763</v>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
@@ -9738,53 +9734,261 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN42" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
           <t>L2-3</t>
         </is>
       </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>85.335609</t>
-        </is>
+      <c r="AP42" s="3" t="n">
+        <v>85.33560900000001</v>
       </c>
       <c r="AQ42" s="3" t="inlineStr"/>
       <c r="AR42" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>6h 11m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
           <t>Case : 6G router setup request  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS42" s="3" t="inlineStr">
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX42" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 4:19 PM</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV  SETBOX ISSUE  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>IPTV  SETBOX ISSUE</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353893</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Gita bhujel</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>Gita bhujel</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>9808751233</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:19:05 PM</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>9808751233</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 12:47:20 PM</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:19:05 PM</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
+          <t>27.746223</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA43" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC43" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr"/>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>dhapasi height, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr"/>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr"/>
+      <c r="AI43" s="3" t="inlineStr">
+        <is>
+          <t>03:32 hour</t>
+        </is>
+      </c>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr"/>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Yadav (L1 Support)</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>L4-4</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr">
+        <is>
+          <t>85.330001</t>
+        </is>
+      </c>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV  SETBOX ISSUE  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT42" s="3" t="inlineStr">
-        <is>
-          <t>6h 11m</t>
-        </is>
-      </c>
-      <c r="AU42" s="3" t="inlineStr">
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>3h 31m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV42" s="3" t="inlineStr">
-        <is>
-          <t>Case : 6G router setup request  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW42" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="AX42" s="3" t="inlineStr">
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV  SETBOX ISSUE  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX43" s="3" t="inlineStr">
         <is>
           <t>Sanjeev Giri</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>29.2%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.6%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>16</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>80.8%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.2%</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0</v>
@@ -856,10 +856,10 @@
         <v>6</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -893,11 +893,11 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Download &amp; Upload Speed Issue</t>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -906,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
@@ -921,11 +921,11 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Audio &amp; Video Syn Issue</t>
+          <t>Download &amp; Upload Speed Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -934,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>NETTV-No internet connection in STB</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -962,10 +962,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -977,20 +977,20 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>0</v>
@@ -1005,14 +1005,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Query For Secondary Router /Repeater</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -1033,11 +1033,11 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>Query For Secondary Router /Repeater</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>0</v>
@@ -1052,7 +1052,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>1</v>
@@ -1061,7 +1061,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Channel buffering,feeze issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -1089,7 +1089,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
@@ -1105,10 +1105,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="H11" s="6" t="n">
         <v>1</v>
@@ -1117,7 +1117,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
@@ -1143,31 +1143,59 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C13" s="4" t="n">
+      <c r="B14" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D14" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E14" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="F13" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>37</v>
+      <c r="F14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1181,7 +1209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX43"/>
+  <dimension ref="A1:AX49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1194,10 +1222,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="38" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="38" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -9849,10 +9877,8 @@
           <t>Gita bhujel</t>
         </is>
       </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>9808751233</t>
-        </is>
+      <c r="O43" s="3" t="n">
+        <v>9808751233</v>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
@@ -9887,10 +9913,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t>27.746223</t>
-        </is>
+      <c r="Y43" s="3" t="n">
+        <v>27.746223</v>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
@@ -9942,55 +9966,1347 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN43" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
           <t>L4-4</t>
         </is>
       </c>
-      <c r="AP43" s="3" t="inlineStr">
-        <is>
-          <t>85.330001</t>
-        </is>
+      <c r="AP43" s="3" t="n">
+        <v>85.330001</v>
       </c>
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>3h 31m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
           <t>Case : IPTV  SETBOX ISSUE  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS43" s="3" t="inlineStr">
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX43" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 4:36 PM</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353808</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>dorje lama</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>dorje lama</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>9849177135</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:36:50 PM</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>BKT9849177135</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:48:04 AM</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:36:50 PM</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA44" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB44" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC44" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD44" s="3" t="inlineStr"/>
+      <c r="AE44" s="3" t="inlineStr">
+        <is>
+          <t>kamalbinayak , Bhaktapur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF44" s="3" t="inlineStr">
+        <is>
+          <t>bdc@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG44" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-No internet connection in STB</t>
+        </is>
+      </c>
+      <c r="AH44" s="3" t="inlineStr"/>
+      <c r="AI44" s="3" t="inlineStr">
+        <is>
+          <t>04:48 hour</t>
+        </is>
+      </c>
+      <c r="AJ44" s="3" t="inlineStr"/>
+      <c r="AK44" s="3" t="inlineStr"/>
+      <c r="AL44" s="3" t="inlineStr">
+        <is>
+          <t>Rejina Shrestha</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>L57-6</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ44" s="3" t="inlineStr"/>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT43" s="3" t="inlineStr">
-        <is>
-          <t>3h 31m</t>
-        </is>
-      </c>
-      <c r="AU43" s="3" t="inlineStr">
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>4h 48m</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV43" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV  SETBOX ISSUE  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW43" s="3" t="inlineStr">
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
         </is>
       </c>
-      <c r="AX43" s="3" t="inlineStr">
-        <is>
-          <t>Sanjeev Giri</t>
+      <c r="AX44" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 4:37 PM</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353582</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Sapana Tamang</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Sapana Tamang</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>9840008359</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:41:23 AM</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>9840008359</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:41:23 AM</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:37:22 PM</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t>27.68641</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA45" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC45" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr"/>
+      <c r="AE45" s="3" t="inlineStr">
+        <is>
+          <t>Chandragiri Municipality Ward No. 6 Office Details from Google Maps M6QG+77W, Chandragiri 44600, Ba</t>
+        </is>
+      </c>
+      <c r="AF45" s="3" t="inlineStr">
+        <is>
+          <t>saphaltmang555@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG45" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="inlineStr"/>
+      <c r="AI45" s="3" t="inlineStr">
+        <is>
+          <t>06:36 hour</t>
+        </is>
+      </c>
+      <c r="AJ45" s="3" t="inlineStr"/>
+      <c r="AK45" s="3" t="inlineStr"/>
+      <c r="AL45" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>CDB365</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr">
+        <is>
+          <t>85.226968</t>
+        </is>
+      </c>
+      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>6h 55m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>6h 55m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX45" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 4:36 PM</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353582</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>Sapana Tamang</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>Sapana Tamang</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>9840008359</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:41:23 AM</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>9840008359</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:41:23 AM</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:37:22 PM</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t>27.68641</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA46" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB46" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC46" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr"/>
+      <c r="AE46" s="3" t="inlineStr">
+        <is>
+          <t>Chandragiri Municipality Ward No. 6 Office Details from Google Maps M6QG+77W, Chandragiri 44600, Ba</t>
+        </is>
+      </c>
+      <c r="AF46" s="3" t="inlineStr">
+        <is>
+          <t>saphaltmang555@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG46" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH46" s="3" t="inlineStr"/>
+      <c r="AI46" s="3" t="inlineStr">
+        <is>
+          <t>06:36 hour</t>
+        </is>
+      </c>
+      <c r="AJ46" s="3" t="inlineStr"/>
+      <c r="AK46" s="3" t="inlineStr"/>
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>CDB365</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr">
+        <is>
+          <t>85.226968</t>
+        </is>
+      </c>
+      <c r="AQ46" s="3" t="inlineStr"/>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>6h 55m</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>6h 55m</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX46" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 4:32 PM</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353091</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>Alternative Herbal Products Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>Alternative Herbal Products Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>9849215450</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 06:08:21 PM</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr">
+        <is>
+          <t>9849215450</t>
+        </is>
+      </c>
+      <c r="V47" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 06:08:21 PM</t>
+        </is>
+      </c>
+      <c r="W47" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:32:01 PM</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y47" s="3" t="inlineStr">
+        <is>
+          <t>27.68618</t>
+        </is>
+      </c>
+      <c r="Z47" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA47" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB47" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC47" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD47" s="3" t="inlineStr"/>
+      <c r="AE47" s="3" t="inlineStr">
+        <is>
+          <t>Balkhu Opposite of BPA college, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF47" s="3" t="inlineStr">
+        <is>
+          <t>vision.ghimire96@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG47" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH47" s="3" t="inlineStr"/>
+      <c r="AI47" s="3" t="inlineStr">
+        <is>
+          <t>08:24 hour</t>
+        </is>
+      </c>
+      <c r="AJ47" s="3" t="inlineStr"/>
+      <c r="AK47" s="3" t="inlineStr"/>
+      <c r="AL47" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO47" s="3" t="inlineStr">
+        <is>
+          <t>CDB164</t>
+        </is>
+      </c>
+      <c r="AP47" s="3" t="inlineStr">
+        <is>
+          <t>85.29338</t>
+        </is>
+      </c>
+      <c r="AQ47" s="3" t="inlineStr"/>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>22h 23m</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>22h 23m</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 4:31 PM</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353091</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>Alternative Herbal Products Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>Alternative Herbal Products Pvt Ltd</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>9849215450</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 06:08:21 PM</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>9849215450</t>
+        </is>
+      </c>
+      <c r="V48" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 06:08:21 PM</t>
+        </is>
+      </c>
+      <c r="W48" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:32:01 PM</t>
+        </is>
+      </c>
+      <c r="X48" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y48" s="3" t="inlineStr">
+        <is>
+          <t>27.68618</t>
+        </is>
+      </c>
+      <c r="Z48" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA48" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB48" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC48" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD48" s="3" t="inlineStr"/>
+      <c r="AE48" s="3" t="inlineStr">
+        <is>
+          <t>Balkhu Opposite of BPA college, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF48" s="3" t="inlineStr">
+        <is>
+          <t>vision.ghimire96@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG48" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH48" s="3" t="inlineStr"/>
+      <c r="AI48" s="3" t="inlineStr">
+        <is>
+          <t>08:24 hour</t>
+        </is>
+      </c>
+      <c r="AJ48" s="3" t="inlineStr"/>
+      <c r="AK48" s="3" t="inlineStr"/>
+      <c r="AL48" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM48" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN48" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO48" s="3" t="inlineStr">
+        <is>
+          <t>CDB164</t>
+        </is>
+      </c>
+      <c r="AP48" s="3" t="inlineStr">
+        <is>
+          <t>85.29338</t>
+        </is>
+      </c>
+      <c r="AQ48" s="3" t="inlineStr"/>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>22h 23m</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>22h 23m</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX48" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 4:30 PM</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350037</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>S K Mustafa</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>S K Mustafa</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>9818066040</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 01:58:27 PM</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>9818066040</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 01:58:27 PM</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 04:30:42 PM</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="inlineStr">
+        <is>
+          <t>27.707037</t>
+        </is>
+      </c>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr">
+        <is>
+          <t>Nera Jagat Sundar Bwonekuthi Secondary School,P842+XPF, ????????? ?????? ???, Kathmandu 44600, Bagma</t>
+        </is>
+      </c>
+      <c r="AF49" s="3" t="inlineStr">
+        <is>
+          <t>ali.sksabir@yahoo.com</t>
+        </is>
+      </c>
+      <c r="AG49" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH49" s="3" t="inlineStr"/>
+      <c r="AI49" s="3" t="inlineStr">
+        <is>
+          <t>08:32 hour</t>
+        </is>
+      </c>
+      <c r="AJ49" s="3" t="inlineStr"/>
+      <c r="AK49" s="3" t="inlineStr"/>
+      <c r="AL49" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>1,12</t>
+        </is>
+      </c>
+      <c r="AP49" s="3" t="inlineStr">
+        <is>
+          <t>85.301797</t>
+        </is>
+      </c>
+      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>3d 2h 32m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>3d 2h 32m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -1255,7 +1255,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -10071,20 +10071,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M44" s="3" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr">
         <is>
           <t>dorje lama</t>
         </is>
       </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>9849177135</t>
-        </is>
+      <c r="O44" s="3" t="n">
+        <v>9849177135</v>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
@@ -10119,10 +10113,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y44" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
@@ -10178,25 +10170,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN44" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
           <t>L57-6</t>
         </is>
       </c>
-      <c r="AP44" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ44" s="3" t="inlineStr"/>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
@@ -10297,10 +10285,8 @@
           <t>Sapana Tamang</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>9840008359</t>
-        </is>
+      <c r="O45" s="3" t="n">
+        <v>9840008359</v>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -10335,10 +10321,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t>27.68641</t>
-        </is>
+      <c r="Y45" s="3" t="n">
+        <v>27.68641</v>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
@@ -10394,25 +10378,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN45" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
           <t>CDB365</t>
         </is>
       </c>
-      <c r="AP45" s="3" t="inlineStr">
-        <is>
-          <t>85.226968</t>
-        </is>
+      <c r="AP45" s="3" t="n">
+        <v>85.226968</v>
       </c>
       <c r="AQ45" s="3" t="inlineStr"/>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
@@ -10513,10 +10493,8 @@
           <t>Sapana Tamang</t>
         </is>
       </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>9840008359</t>
-        </is>
+      <c r="O46" s="3" t="n">
+        <v>9840008359</v>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
@@ -10551,10 +10529,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t>27.68641</t>
-        </is>
+      <c r="Y46" s="3" t="n">
+        <v>27.68641</v>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
@@ -10610,25 +10586,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN46" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
           <t>CDB365</t>
         </is>
       </c>
-      <c r="AP46" s="3" t="inlineStr">
-        <is>
-          <t>85.226968</t>
-        </is>
+      <c r="AP46" s="3" t="n">
+        <v>85.226968</v>
       </c>
       <c r="AQ46" s="3" t="inlineStr"/>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
@@ -10729,10 +10701,8 @@
           <t>Alternative Herbal Products Pvt Ltd</t>
         </is>
       </c>
-      <c r="O47" s="3" t="inlineStr">
-        <is>
-          <t>9849215450</t>
-        </is>
+      <c r="O47" s="3" t="n">
+        <v>9849215450</v>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
@@ -10767,10 +10737,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y47" s="3" t="inlineStr">
-        <is>
-          <t>27.68618</t>
-        </is>
+      <c r="Y47" s="3" t="n">
+        <v>27.68618</v>
       </c>
       <c r="Z47" s="3" t="inlineStr">
         <is>
@@ -10826,25 +10794,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN47" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN47" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
           <t>CDB164</t>
         </is>
       </c>
-      <c r="AP47" s="3" t="inlineStr">
-        <is>
-          <t>85.29338</t>
-        </is>
+      <c r="AP47" s="3" t="n">
+        <v>85.29338</v>
       </c>
       <c r="AQ47" s="3" t="inlineStr"/>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
@@ -10945,10 +10909,8 @@
           <t>Alternative Herbal Products Pvt Ltd</t>
         </is>
       </c>
-      <c r="O48" s="3" t="inlineStr">
-        <is>
-          <t>9849215450</t>
-        </is>
+      <c r="O48" s="3" t="n">
+        <v>9849215450</v>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
@@ -10983,10 +10945,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y48" s="3" t="inlineStr">
-        <is>
-          <t>27.68618</t>
-        </is>
+      <c r="Y48" s="3" t="n">
+        <v>27.68618</v>
       </c>
       <c r="Z48" s="3" t="inlineStr">
         <is>
@@ -11042,25 +11002,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN48" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN48" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
           <t>CDB164</t>
         </is>
       </c>
-      <c r="AP48" s="3" t="inlineStr">
-        <is>
-          <t>85.29338</t>
-        </is>
+      <c r="AP48" s="3" t="n">
+        <v>85.29338</v>
       </c>
       <c r="AQ48" s="3" t="inlineStr"/>
       <c r="AR48" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS48" s="3" t="inlineStr">
@@ -11161,10 +11117,8 @@
           <t>S K Mustafa</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>9818066040</t>
-        </is>
+      <c r="O49" s="3" t="n">
+        <v>9818066040</v>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
@@ -11199,10 +11153,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y49" s="3" t="inlineStr">
-        <is>
-          <t>27.707037</t>
-        </is>
+      <c r="Y49" s="3" t="n">
+        <v>27.707037</v>
       </c>
       <c r="Z49" s="3" t="inlineStr">
         <is>
@@ -11258,25 +11210,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN49" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
           <t>1,12</t>
         </is>
       </c>
-      <c r="AP49" s="3" t="inlineStr">
-        <is>
-          <t>85.301797</t>
-        </is>
+      <c r="AP49" s="3" t="n">
+        <v>85.30179699999999</v>
       </c>
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS49" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>90.9%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>76.0%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>32.0%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>14.0%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>52.0%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
         <v>11</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>6</v>
@@ -859,7 +859,7 @@
         <v>3</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -1186,7 +1186,7 @@
         <v>11</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>10</v>
@@ -1195,7 +1195,7 @@
         <v>5</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1209,7 +1209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX49"/>
+  <dimension ref="A1:AX51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1255,7 +1255,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -11258,6 +11258,438 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 5:03 PM</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>Router upgrade</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352766</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>Sonic Napit</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>Sonic Napit</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>9841304879</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 05:03:23 PM</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>9880756943</t>
+        </is>
+      </c>
+      <c r="V50" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:51:12 PM</t>
+        </is>
+      </c>
+      <c r="W50" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 05:03:23 PM</t>
+        </is>
+      </c>
+      <c r="X50" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y50" s="3" t="inlineStr">
+        <is>
+          <t>27.71567</t>
+        </is>
+      </c>
+      <c r="Z50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA50" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB50" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC50" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD50" s="3" t="inlineStr"/>
+      <c r="AE50" s="3" t="inlineStr">
+        <is>
+          <t>Behind Bishnu Bimala Kunja, Near Nagarkot dairy- Naya Basti-  Kumarigal Boudha- 6, Bagmati, Central,</t>
+        </is>
+      </c>
+      <c r="AF50" s="3" t="inlineStr">
+        <is>
+          <t>sonicnapit0104@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG50" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH50" s="3" t="inlineStr"/>
+      <c r="AI50" s="3" t="inlineStr">
+        <is>
+          <t>12:12 hour</t>
+        </is>
+      </c>
+      <c r="AJ50" s="3" t="inlineStr"/>
+      <c r="AK50" s="3" t="inlineStr"/>
+      <c r="AL50" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM50" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN50" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO50" s="3" t="inlineStr">
+        <is>
+          <t>L53-2</t>
+        </is>
+      </c>
+      <c r="AP50" s="3" t="inlineStr">
+        <is>
+          <t>85.36795</t>
+        </is>
+      </c>
+      <c r="AQ50" s="3" t="inlineStr"/>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 12m</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX50" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 5:02 PM</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>Router upgrade</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352766</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>Sonic Napit</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>Sonic Napit</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>9841304879</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr"/>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 05:03:23 PM</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr"/>
+      <c r="T51" s="3" t="inlineStr"/>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>9880756943</t>
+        </is>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 02:51:12 PM</t>
+        </is>
+      </c>
+      <c r="W51" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 05:03:23 PM</t>
+        </is>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y51" s="3" t="inlineStr">
+        <is>
+          <t>27.71567</t>
+        </is>
+      </c>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA51" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB51" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC51" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD51" s="3" t="inlineStr"/>
+      <c r="AE51" s="3" t="inlineStr">
+        <is>
+          <t>Behind Bishnu Bimala Kunja, Near Nagarkot dairy- Naya Basti-  Kumarigal Boudha- 6, Bagmati, Central,</t>
+        </is>
+      </c>
+      <c r="AF51" s="3" t="inlineStr">
+        <is>
+          <t>sonicnapit0104@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG51" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH51" s="3" t="inlineStr"/>
+      <c r="AI51" s="3" t="inlineStr">
+        <is>
+          <t>12:12 hour</t>
+        </is>
+      </c>
+      <c r="AJ51" s="3" t="inlineStr"/>
+      <c r="AK51" s="3" t="inlineStr"/>
+      <c r="AL51" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO51" s="3" t="inlineStr">
+        <is>
+          <t>L53-2</t>
+        </is>
+      </c>
+      <c r="AP51" s="3" t="inlineStr">
+        <is>
+          <t>85.36795</t>
+        </is>
+      </c>
+      <c r="AQ51" s="3" t="inlineStr"/>
+      <c r="AR51" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 12m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>7</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>76.5%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>31.4%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>13.7%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0</v>
@@ -859,7 +859,7 @@
         <v>3</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>1</v>
@@ -1195,7 +1195,7 @@
         <v>5</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1209,7 +1209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX51"/>
+  <dimension ref="A1:AX52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -11325,10 +11325,8 @@
           <t>Sonic Napit</t>
         </is>
       </c>
-      <c r="O50" s="3" t="inlineStr">
-        <is>
-          <t>9841304879</t>
-        </is>
+      <c r="O50" s="3" t="n">
+        <v>9841304879</v>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
@@ -11363,10 +11361,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y50" s="3" t="inlineStr">
-        <is>
-          <t>27.71567</t>
-        </is>
+      <c r="Y50" s="3" t="n">
+        <v>27.71567</v>
       </c>
       <c r="Z50" s="3" t="inlineStr">
         <is>
@@ -11422,25 +11418,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN50" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN50" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
           <t>L53-2</t>
         </is>
       </c>
-      <c r="AP50" s="3" t="inlineStr">
-        <is>
-          <t>85.36795</t>
-        </is>
+      <c r="AP50" s="3" t="n">
+        <v>85.36794999999999</v>
       </c>
       <c r="AQ50" s="3" t="inlineStr"/>
       <c r="AR50" s="3" t="inlineStr">
         <is>
-          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS50" s="3" t="inlineStr">
@@ -11541,10 +11533,8 @@
           <t>Sonic Napit</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
-          <t>9841304879</t>
-        </is>
+      <c r="O51" s="3" t="n">
+        <v>9841304879</v>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
@@ -11579,10 +11569,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y51" s="3" t="inlineStr">
-        <is>
-          <t>27.71567</t>
-        </is>
+      <c r="Y51" s="3" t="n">
+        <v>27.71567</v>
       </c>
       <c r="Z51" s="3" t="inlineStr">
         <is>
@@ -11638,47 +11626,43 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN51" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN51" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
           <t>L53-2</t>
         </is>
       </c>
-      <c r="AP51" s="3" t="inlineStr">
-        <is>
-          <t>85.36795</t>
-        </is>
+      <c r="AP51" s="3" t="n">
+        <v>85.36794999999999</v>
       </c>
       <c r="AQ51" s="3" t="inlineStr"/>
       <c r="AR51" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 12m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
           <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS51" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT51" s="3" t="inlineStr">
-        <is>
-          <t>1d 2h 12m</t>
-        </is>
-      </c>
-      <c r="AU51" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV51" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="AW51" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -11687,6 +11671,214 @@
       <c r="AX51" s="3" t="inlineStr">
         <is>
           <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 5:25 PM</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1352880</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>Anil Pandey</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>Anil Pandey</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>9867339967</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr"/>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:04:27 PM</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr"/>
+      <c r="T52" s="3" t="inlineStr"/>
+      <c r="U52" s="3" t="inlineStr">
+        <is>
+          <t>KLK9867339967</t>
+        </is>
+      </c>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04:04:27 PM</t>
+        </is>
+      </c>
+      <c r="W52" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 05:25:36 PM</t>
+        </is>
+      </c>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y52" s="3" t="inlineStr"/>
+      <c r="Z52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA52" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB52" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC52" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD52" s="3" t="inlineStr"/>
+      <c r="AE52" s="3" t="inlineStr">
+        <is>
+          <t>Kirtipur Hospital, Kirtipur Ring Rd, Kathmandu 44618, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF52" s="3" t="inlineStr">
+        <is>
+          <t>apyfx.np@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG52" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH52" s="3" t="inlineStr"/>
+      <c r="AI52" s="3" t="inlineStr">
+        <is>
+          <t>11:21 hour</t>
+        </is>
+      </c>
+      <c r="AJ52" s="3" t="inlineStr"/>
+      <c r="AK52" s="3" t="inlineStr"/>
+      <c r="AL52" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM52" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN52" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO52" s="3" t="inlineStr">
+        <is>
+          <t>CDB191</t>
+        </is>
+      </c>
+      <c r="AP52" s="3" t="inlineStr"/>
+      <c r="AQ52" s="3" t="inlineStr"/>
+      <c r="AR52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 21m</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 21m</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX52" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>75.5%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>12</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>32.1%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.2%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>82.1%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>52.8%</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Audio &amp; Video Syn Issue</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -906,16 +906,16 @@
         <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -977,7 +977,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>NETTV-Audio &amp; Video Syn Issue</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -1005,20 +1005,20 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -1089,14 +1089,14 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Channel buffering,feeze issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>0</v>
@@ -1108,7 +1108,7 @@
         <v>0</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="6" t="n">
         <v>1</v>
@@ -1117,7 +1117,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
@@ -1133,10 +1133,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>1</v>
@@ -1145,7 +1145,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
@@ -1189,13 +1189,13 @@
         <v>9</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G14" s="4" t="n">
         <v>5</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1209,7 +1209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX52"/>
+  <dimension ref="A1:AX54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -11741,10 +11741,8 @@
           <t>Anil Pandey</t>
         </is>
       </c>
-      <c r="O52" s="3" t="inlineStr">
-        <is>
-          <t>9867339967</t>
-        </is>
+      <c r="O52" s="3" t="n">
+        <v>9867339967</v>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
@@ -11834,10 +11832,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN52" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN52" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO52" s="3" t="inlineStr">
         <is>
@@ -11848,29 +11844,29 @@
       <c r="AQ52" s="3" t="inlineStr"/>
       <c r="AR52" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 21m</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 21m</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS52" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 21m</t>
-        </is>
-      </c>
-      <c r="AT52" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 21m</t>
-        </is>
-      </c>
-      <c r="AU52" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV52" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW52" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -11879,6 +11875,422 @@
       <c r="AX52" s="3" t="inlineStr">
         <is>
           <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 5:37 PM</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Case : worst internet service   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>worst internet service</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350654</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Shrestha</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Shrestha</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>9700971170</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr"/>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 09:53:45 PM</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr"/>
+      <c r="T53" s="3" t="inlineStr"/>
+      <c r="U53" s="3" t="inlineStr">
+        <is>
+          <t>9823190890R</t>
+        </is>
+      </c>
+      <c r="V53" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 07:40:24 PM</t>
+        </is>
+      </c>
+      <c r="W53" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 05:37:27 PM</t>
+        </is>
+      </c>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y53" s="3" t="inlineStr">
+        <is>
+          <t>27.66368,</t>
+        </is>
+      </c>
+      <c r="Z53" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA53" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB53" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC53" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD53" s="3" t="inlineStr">
+        <is>
+          <t>Box End</t>
+        </is>
+      </c>
+      <c r="AE53" s="3" t="inlineStr">
+        <is>
+          <t>ala Futsal &amp; Recreational Center Details from Google Maps Unnamed Road, M87P+5VQ, ?????????? 44700 +</t>
+        </is>
+      </c>
+      <c r="AF53" s="3" t="inlineStr">
+        <is>
+          <t>rs1460451@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG53" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH53" s="3" t="inlineStr"/>
+      <c r="AI53" s="3" t="inlineStr"/>
+      <c r="AJ53" s="3" t="inlineStr"/>
+      <c r="AK53" s="3" t="inlineStr"/>
+      <c r="AL53" s="3" t="inlineStr"/>
+      <c r="AM53" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN53" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO53" s="3" t="inlineStr">
+        <is>
+          <t>1,15</t>
+        </is>
+      </c>
+      <c r="AP53" s="3" t="inlineStr">
+        <is>
+          <t>85.33794</t>
+        </is>
+      </c>
+      <c r="AQ53" s="3" t="inlineStr"/>
+      <c r="AR53" s="3" t="inlineStr">
+        <is>
+          <t>Case : worst internet service   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS53" s="3" t="inlineStr">
+        <is>
+          <t>19h 43m</t>
+        </is>
+      </c>
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 57m</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV53" s="3" t="inlineStr">
+        <is>
+          <t>Case : worst internet service   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX53" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 5:35 PM</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1353804</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>bindu bhattrai</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>bindu bhattrai</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>9841881780</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr"/>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 05:35:45 PM</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="inlineStr"/>
+      <c r="T54" s="3" t="inlineStr"/>
+      <c r="U54" s="3" t="inlineStr">
+        <is>
+          <t>9841881780</t>
+        </is>
+      </c>
+      <c r="V54" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 11:46:37 AM</t>
+        </is>
+      </c>
+      <c r="W54" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 05:35:45 PM</t>
+        </is>
+      </c>
+      <c r="X54" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y54" s="3" t="inlineStr"/>
+      <c r="Z54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA54" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB54" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC54" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD54" s="3" t="inlineStr"/>
+      <c r="AE54" s="3" t="inlineStr">
+        <is>
+          <t>balkot, shanti chock, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF54" s="3" t="inlineStr"/>
+      <c r="AG54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH54" s="3" t="inlineStr"/>
+      <c r="AI54" s="3" t="inlineStr">
+        <is>
+          <t>05:49 hour</t>
+        </is>
+      </c>
+      <c r="AJ54" s="3" t="inlineStr"/>
+      <c r="AK54" s="3" t="inlineStr"/>
+      <c r="AL54" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM54" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN54" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO54" s="3" t="inlineStr">
+        <is>
+          <t>L53-8</t>
+        </is>
+      </c>
+      <c r="AP54" s="3" t="inlineStr"/>
+      <c r="AQ54" s="3" t="inlineStr"/>
+      <c r="AR54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS54" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT54" s="3" t="inlineStr">
+        <is>
+          <t>5h 49m</t>
+        </is>
+      </c>
+      <c r="AU54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW54" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX54" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>10</v>
-      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>91.7%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>75.9%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>31.5%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.0%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>82.8%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>53.7%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
         <v>11</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>6</v>
@@ -859,7 +859,7 @@
         <v>3</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -1186,7 +1186,7 @@
         <v>11</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>11</v>
@@ -1195,7 +1195,7 @@
         <v>5</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1209,7 +1209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX54"/>
+  <dimension ref="A1:AX55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -11945,10 +11945,8 @@
           <t>Roshan Shrestha</t>
         </is>
       </c>
-      <c r="O53" s="3" t="inlineStr">
-        <is>
-          <t>9700971170</t>
-        </is>
+      <c r="O53" s="3" t="n">
+        <v>9700971170</v>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
@@ -12038,25 +12036,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN53" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN53" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
           <t>1,15</t>
         </is>
       </c>
-      <c r="AP53" s="3" t="inlineStr">
-        <is>
-          <t>85.33794</t>
-        </is>
+      <c r="AP53" s="3" t="n">
+        <v>85.33794</v>
       </c>
       <c r="AQ53" s="3" t="inlineStr"/>
       <c r="AR53" s="3" t="inlineStr">
         <is>
-          <t>Case : worst internet service   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS53" s="3" t="inlineStr">
@@ -12157,10 +12151,8 @@
           <t>bindu bhattrai</t>
         </is>
       </c>
-      <c r="O54" s="3" t="inlineStr">
-        <is>
-          <t>9841881780</t>
-        </is>
+      <c r="O54" s="3" t="n">
+        <v>9841881780</v>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
@@ -12246,10 +12238,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN54" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN54" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
@@ -12260,37 +12250,245 @@
       <c r="AQ54" s="3" t="inlineStr"/>
       <c r="AR54" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS54" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT54" s="3" t="inlineStr">
+        <is>
+          <t>5h 49m</t>
+        </is>
+      </c>
+      <c r="AU54" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV54" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS54" s="3" t="inlineStr">
+      <c r="AW54" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX54" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 5:56 PM</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>TKT1354116</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>Rabin Thapa</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>Rabin Thapa</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>9808069533</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr"/>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 05:56:20 PM</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr"/>
+      <c r="T55" s="3" t="inlineStr"/>
+      <c r="U55" s="3" t="inlineStr">
+        <is>
+          <t>9808069533</t>
+        </is>
+      </c>
+      <c r="V55" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 03:54:01 PM</t>
+        </is>
+      </c>
+      <c r="W55" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 05:56:20 PM</t>
+        </is>
+      </c>
+      <c r="X55" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y55" s="3" t="inlineStr"/>
+      <c r="Z55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA55" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB55" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC55" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD55" s="3" t="inlineStr"/>
+      <c r="AE55" s="3" t="inlineStr">
+        <is>
+          <t>Nayabasti youth club, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF55" s="3" t="inlineStr">
+        <is>
+          <t>rabinthapa422@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG55" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH55" s="3" t="inlineStr"/>
+      <c r="AI55" s="3" t="inlineStr">
+        <is>
+          <t>02:02 hour</t>
+        </is>
+      </c>
+      <c r="AJ55" s="3" t="inlineStr"/>
+      <c r="AK55" s="3" t="inlineStr"/>
+      <c r="AL55" s="3" t="inlineStr">
+        <is>
+          <t>Kusum Gurung</t>
+        </is>
+      </c>
+      <c r="AM55" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN55" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO55" s="3" t="inlineStr">
+        <is>
+          <t>L24-8</t>
+        </is>
+      </c>
+      <c r="AP55" s="3" t="inlineStr"/>
+      <c r="AQ55" s="3" t="inlineStr"/>
+      <c r="AR55" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT54" s="3" t="inlineStr">
-        <is>
-          <t>5h 49m</t>
-        </is>
-      </c>
-      <c r="AU54" s="3" t="inlineStr">
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>2h 2m</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV54" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW54" s="3" t="inlineStr">
+      <c r="AV55" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW55" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX54" s="3" t="inlineStr">
-        <is>
-          <t>Shashikant Chaudhary</t>
+      <c r="AX55" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_01_Oct_2026.xlsx
@@ -1255,7 +1255,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -12351,10 +12351,8 @@
           <t>Rabin Thapa</t>
         </is>
       </c>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
-          <t>9808069533</t>
-        </is>
+      <c r="O55" s="3" t="n">
+        <v>9808069533</v>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
@@ -12444,10 +12442,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN55" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN55" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
@@ -12458,7 +12454,7 @@
       <c r="AQ55" s="3" t="inlineStr"/>
       <c r="AR55" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS55" s="3" t="inlineStr">
